--- a/mosip_master/xlsx/doc_category.xlsx
+++ b/mosip_master/xlsx/doc_category.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FCF303-F463-416D-A83D-89FEDAC654E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56E5A5C-F1D1-41EC-AEE7-D1778F0F75D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="doc_category" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">doc_category!$A$1:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">doc_category!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="96">
   <si>
     <t>code</t>
   </si>
@@ -190,12 +190,6 @@
     <t>Proof Of Court Order</t>
   </si>
   <si>
-    <t>OTH03</t>
-  </si>
-  <si>
-    <t>Other Document</t>
-  </si>
-  <si>
     <t>NULL</t>
   </si>
   <si>
@@ -205,9 +199,6 @@
     <t>Proof of Abandonment</t>
   </si>
   <si>
-    <t>Proof of birth</t>
-  </si>
-  <si>
     <t>POIS</t>
   </si>
   <si>
@@ -235,36 +226,18 @@
     <t>POOSD</t>
   </si>
   <si>
-    <t>Proof of other supporting document Issued by Government</t>
-  </si>
-  <si>
-    <t>Proof of other supporting document issued by govt</t>
-  </si>
-  <si>
     <t>POPC</t>
   </si>
   <si>
     <t>Proof of Police Confirmation</t>
   </si>
   <si>
-    <t>PORARS</t>
-  </si>
-  <si>
-    <t>Proof of residence and registration supportÂ </t>
-  </si>
-  <si>
-    <t>Residence and Registration supportÂ </t>
-  </si>
-  <si>
     <t>Authorization Documents</t>
   </si>
   <si>
     <t>POSD</t>
   </si>
   <si>
-    <t>Proof of other supporting document</t>
-  </si>
-  <si>
     <t>POL</t>
   </si>
   <si>
@@ -278,6 +251,66 @@
   </si>
   <si>
     <t>Proof of Physical Application Form (Required for Walk-In Applications)</t>
+  </si>
+  <si>
+    <t>BCOSP</t>
+  </si>
+  <si>
+    <t>CAOR</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>COREP</t>
+  </si>
+  <si>
+    <t>NCOSP</t>
+  </si>
+  <si>
+    <t>PBREP</t>
+  </si>
+  <si>
+    <t>PPOSP</t>
+  </si>
+  <si>
+    <t>WEAFA</t>
+  </si>
+  <si>
+    <t>Ex-servicemen certificate</t>
+  </si>
+  <si>
+    <t>Proof date of birth of the person</t>
+  </si>
+  <si>
+    <t>Proof of Other Supporting Document Issued by Govt</t>
+  </si>
+  <si>
+    <t>Proof of Other Supporting Document</t>
+  </si>
+  <si>
+    <t>Copies of birth certificates of self parents or grandparents</t>
+  </si>
+  <si>
+    <t>Care Order</t>
+  </si>
+  <si>
+    <t>Court Report</t>
+  </si>
+  <si>
+    <t>Naturalisation Certificate of self parents</t>
+  </si>
+  <si>
+    <t>Probation Report</t>
+  </si>
+  <si>
+    <t>Previous passports of self, parents, or grandparents</t>
+  </si>
+  <si>
+    <t>Welfare and Family</t>
+  </si>
+  <si>
+    <t>Welfare and family</t>
   </si>
 </sst>
 </file>
@@ -768,11 +801,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -1149,12 +1181,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAEBCC2-B773-4107-AFE8-13DD4FA99942}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1195,31 +1227,31 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1">
-        <v>45634.749305555553</v>
+      <c r="G2" s="2">
+        <v>45565.669496388888</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1">
-        <v>45634.749305555553</v>
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>55</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -1227,13 +1259,13 @@
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1244,14 +1276,14 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2">
-        <v>45565.669496388888</v>
+      <c r="G3" s="1">
+        <v>45634.749305555553</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" t="s">
-        <v>57</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45634.749305555553</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -1259,13 +1291,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1291,19 +1323,19 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1323,19 +1355,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1355,19 +1387,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -1387,13 +1419,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1419,13 +1451,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1451,13 +1483,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1483,13 +1515,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1515,13 +1547,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1547,13 +1579,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1562,13 +1594,13 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2">
         <v>45590.316647199077</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2">
         <v>45590.316859212966</v>
@@ -1579,13 +1611,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -1596,14 +1628,8 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="2">
-        <v>45614.50859125</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="2">
-        <v>45614.508798113427</v>
+      <c r="G14" s="1">
+        <v>45516.749305555553</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1611,13 +1637,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1628,14 +1654,14 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="1">
-        <v>45516.749305555553</v>
+      <c r="G15" s="2">
+        <v>45614.50859125</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="1">
-        <v>45634.749305555553</v>
+      <c r="I15" s="2">
+        <v>45614.508798113427</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -1643,13 +1669,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -1663,25 +1689,19 @@
       <c r="G16" s="1">
         <v>45516.749305555553</v>
       </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="1">
-        <v>45634.749305555553</v>
-      </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -1698,8 +1718,8 @@
       <c r="H17" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="2">
-        <v>45557.385132488424</v>
+      <c r="I17" s="1">
+        <v>45634.749305555553</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -1707,13 +1727,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -1724,14 +1744,14 @@
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="2">
-        <v>45546.402661550928</v>
+      <c r="G18" s="1">
+        <v>45516.749305555553</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="2">
-        <v>45546.40284412037</v>
+      <c r="I18" s="1">
+        <v>45634.749305555553</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -1739,13 +1759,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1754,16 +1774,16 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45560.544703749998</v>
+        <v>16</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45516.749305555553</v>
       </c>
       <c r="H19" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="I19" s="2">
-        <v>45611.393834247683</v>
+        <v>45557.385132488424</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -1771,13 +1791,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1789,13 +1809,13 @@
         <v>16</v>
       </c>
       <c r="G20" s="2">
-        <v>45614.30081572917</v>
+        <v>45546.402661550928</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" s="2">
-        <v>45614.307864074071</v>
+        <v>45546.40284412037</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1803,13 +1823,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1818,16 +1838,16 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="1">
-        <v>45516.749305555553</v>
+        <v>60</v>
+      </c>
+      <c r="G21" s="2">
+        <v>45560.544703749998</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="1">
-        <v>45634.749305555553</v>
+        <v>60</v>
+      </c>
+      <c r="I21" s="2">
+        <v>45611.393834247683</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -1835,13 +1855,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1852,46 +1872,40 @@
       <c r="F22" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="2">
+        <v>45614.30081572917</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2">
+        <v>45614.307864074071</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1">
         <v>45516.749305555553</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="1">
-        <v>45634.749305555553</v>
-      </c>
-      <c r="J22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="2">
-        <v>45566.254968564812</v>
-      </c>
-      <c r="H23" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="2">
-        <v>45566.258958530096</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -1899,13 +1913,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1919,25 +1933,19 @@
       <c r="G24" s="1">
         <v>45516.749305555553</v>
       </c>
-      <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="1">
-        <v>45634.749305555553</v>
-      </c>
       <c r="J24" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -1963,13 +1971,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1986,8 +1994,8 @@
       <c r="H26" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="2">
-        <v>45574.553623206019</v>
+      <c r="I26" s="1">
+        <v>45634.749305555553</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -1995,13 +2003,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2010,16 +2018,10 @@
         <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="2">
-        <v>45611.391187141206</v>
-      </c>
-      <c r="H27" t="s">
-        <v>63</v>
-      </c>
-      <c r="I27" s="2">
-        <v>45611.391489756941</v>
+        <v>16</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45516.749305497688</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
@@ -2027,13 +2029,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -2045,7 +2047,13 @@
         <v>16</v>
       </c>
       <c r="G28" s="1">
-        <v>45516.749305555553</v>
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="1">
+        <v>45634.749305497688</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -2053,13 +2061,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>84</v>
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -2071,53 +2079,196 @@
         <v>16</v>
       </c>
       <c r="G29" s="1">
-        <v>45516.749305555553</v>
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
         <v>15</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="1">
-        <v>45516.749305555553</v>
+        <v>45516.749305497688</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>72</v>
+      <c r="A31" t="s">
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
         <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="1">
-        <v>45516.749305555553</v>
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45516.749305497688</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/doc_category.xlsx
+++ b/mosip_master/xlsx/doc_category.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56E5A5C-F1D1-41EC-AEE7-D1778F0F75D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60C4F5-8127-42AA-9FAA-42D136A163F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="doc_category" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="98">
   <si>
     <t>code</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>Welfare and family</t>
+  </si>
+  <si>
+    <t>Proof of residence and registration support </t>
+  </si>
+  <si>
+    <t>PORARS</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAEBCC2-B773-4107-AFE8-13DD4FA99942}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -2271,6 +2277,38 @@
         <v>17</v>
       </c>
     </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="1">
+        <v>45516.749305497688</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="1">
+        <v>45634.749305497688</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/mosip_master/xlsx/doc_category.xlsx
+++ b/mosip_master/xlsx/doc_category.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nira-registration\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60C4F5-8127-42AA-9FAA-42D136A163F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0E96EB-FD17-428E-86A8-5CD6098EEABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3F7CCF4D-8218-47FF-82F6-EB07A560EBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="doc_category" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="104">
   <si>
     <t>code</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>PORARS</t>
+  </si>
+  <si>
+    <t>POLCL</t>
+  </si>
+  <si>
+    <t>Proof of LC1 Letter</t>
+  </si>
+  <si>
+    <t>PODMG</t>
+  </si>
+  <si>
+    <t>Damaged Card</t>
+  </si>
+  <si>
+    <t>NID</t>
+  </si>
+  <si>
+    <t>National ID</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAEBCC2-B773-4107-AFE8-13DD4FA99942}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -2309,6 +2327,102 @@
         <v>17</v>
       </c>
     </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45517.749305497688</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="1">
+        <v>45635.749305497688</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45518.749305497688</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="1">
+        <v>45636.749305497688</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="1">
+        <v>45519.749305497688</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1">
+        <v>45637.749305497688</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
